--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,1323 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123515156</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57634</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>541812</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6711741</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123515119</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>541812</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6711741</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123517161</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>541805</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6711682</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123517887</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>541792</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6711744</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123516472</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58159</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>541809</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6711625</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123517424</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>541783</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6711682</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123516006</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57851</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>541818</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6711671</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123515928</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>541818</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6711671</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123517700</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>541783</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6711682</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123515444</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>541772</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6711742</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Röjning runt knärot</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123515597</v>
+        <v>123517088</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517887</v>
+        <v>123515231</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541792</v>
+        <v>541812</v>
       </c>
       <c r="R4" t="n">
-        <v>6711744</v>
+        <v>6711741</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123518009</v>
+        <v>123517424</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1068,43 +1068,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1112,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541812</v>
+        <v>541783</v>
       </c>
       <c r="R5" t="n">
-        <v>6711741</v>
+        <v>6711682</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1147,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1157,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,13 +1158,27 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1190,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123515928</v>
+        <v>123515352</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1225,12 +1231,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1246,10 +1252,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541818</v>
+        <v>541792</v>
       </c>
       <c r="R6" t="n">
-        <v>6711671</v>
+        <v>6711744</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1281,7 +1287,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1291,7 +1297,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Yta 4x4 m</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1306,7 +1317,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1324,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123517424</v>
+        <v>123516006</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>57857</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,20 +1347,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1357,12 +1368,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1372,10 +1391,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541783</v>
+        <v>541818</v>
       </c>
       <c r="R7" t="n">
-        <v>6711682</v>
+        <v>6711671</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1407,7 +1426,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1417,7 +1436,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,22 +1450,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1464,10 +1468,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123517700</v>
+        <v>123516472</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>58165</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,43 +1480,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1520,13 +1516,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541783</v>
+        <v>541809</v>
       </c>
       <c r="R8" t="n">
-        <v>6711682</v>
+        <v>6711625</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1555,7 +1551,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,7 +1561,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,14 +1570,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1598,10 +1588,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123516472</v>
+        <v>123515444</v>
       </c>
       <c r="B9" t="n">
-        <v>58159</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1610,35 +1600,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1646,13 +1644,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541809</v>
+        <v>541772</v>
       </c>
       <c r="R9" t="n">
-        <v>6711625</v>
+        <v>6711742</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1681,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1691,7 +1689,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Röjning runt knärot</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1700,6 +1703,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1718,10 +1722,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123515444</v>
+        <v>123517700</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1753,7 +1757,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1774,10 +1778,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541772</v>
+        <v>541783</v>
       </c>
       <c r="R10" t="n">
-        <v>6711742</v>
+        <v>6711682</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1809,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,12 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Röjning runt knärot</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1836,6 +1835,11 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1852,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123516006</v>
+        <v>123515156</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>57640</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1864,41 +1868,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541818</v>
+        <v>541812</v>
       </c>
       <c r="R11" t="n">
-        <v>6711671</v>
+        <v>6711741</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1985,10 +1985,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123515156</v>
+        <v>123515928</v>
       </c>
       <c r="B12" t="n">
-        <v>57634</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1997,39 +1997,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2037,13 +2041,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541812</v>
+        <v>541818</v>
       </c>
       <c r="R12" t="n">
-        <v>6711741</v>
+        <v>6711671</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2072,7 +2076,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2082,7 +2086,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2091,12 +2095,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2114,10 +2119,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123609210</v>
+        <v>123609341</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2149,7 +2154,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2170,10 +2175,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541647</v>
+        <v>541667</v>
       </c>
       <c r="R13" t="n">
-        <v>6711571</v>
+        <v>6711554</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -2205,7 +2210,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2215,7 +2220,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2251,7 +2256,7 @@
         <v>123606143</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2382,10 +2387,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123610005</v>
+        <v>123609153</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2417,12 +2422,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2434,14 +2439,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541721</v>
+        <v>541647</v>
       </c>
       <c r="R15" t="n">
-        <v>6711610</v>
+        <v>6711571</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2473,7 +2478,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2483,7 +2488,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2516,10 +2521,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123609341</v>
+        <v>123610047</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2551,7 +2556,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2568,14 +2573,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541667</v>
+        <v>541721</v>
       </c>
       <c r="R16" t="n">
-        <v>6711554</v>
+        <v>6711610</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2607,7 +2612,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2617,7 +2622,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2653,7 +2658,7 @@
         <v>123609837</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123516006</v>
+        <v>123515444</v>
       </c>
       <c r="B7" t="n">
-        <v>57857</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,43 +1347,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541818</v>
+        <v>541772</v>
       </c>
       <c r="R7" t="n">
-        <v>6711671</v>
+        <v>6711742</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1436,7 +1436,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Röjning runt knärot</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,13 +1450,9 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1588,10 +1589,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123515444</v>
+        <v>123516006</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1600,43 +1601,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1644,10 +1645,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541772</v>
+        <v>541818</v>
       </c>
       <c r="R9" t="n">
-        <v>6711742</v>
+        <v>6711671</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1679,7 +1680,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,12 +1690,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Röjning runt knärot</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,9 +1699,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -2787,6 +2787,3511 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123775574</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>541671</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6711571</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123776010</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>541669</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6711539</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123780468</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>541805</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6711708</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Alldeles invid körspår.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123779653</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>541788</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6711796</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123775610</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>541674</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6711552</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123776982</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>541650</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6711541</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123778741</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>541760</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6711731</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123776928</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>541657</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6711519</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123777859</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>541727</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6711663</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123772073</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>541829</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6711695</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123777970</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>541726</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6711685</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123778521</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>541722</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6711715</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Alldeles invid en gammal grov gran. Ca 4 meter från bäck.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123771872</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>541839</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6711709</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123779278</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>541778</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6711781</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Invid en  utgrävd bäck</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123772375</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>541819</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6711662</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123778290</v>
+      </c>
+      <c r="B33" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>541709</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6711698</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>I närheten av grävt dike alternativt utgrävd bäck.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123774773</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>541703</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6711589</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123774473</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>541738</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6711622</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123777220</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>541679</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6711585</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123780218</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>541787</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6711764</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123775826</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>541668</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6711539</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123772523</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Torvströmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>541828</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6711635</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123777114</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>541658</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6711551</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123780300</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>541783</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6711759</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123772762</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>541824</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6711621</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Vackert melerade blad</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123777793</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>541741</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6711669</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123609153</v>
+        <v>123610047</v>
       </c>
       <c r="B15" t="n">
         <v>98396</v>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2439,14 +2439,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541647</v>
+        <v>541721</v>
       </c>
       <c r="R15" t="n">
-        <v>6711571</v>
+        <v>6711610</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2521,7 +2521,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123610047</v>
+        <v>123609153</v>
       </c>
       <c r="B16" t="n">
         <v>98396</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2573,14 +2573,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541721</v>
+        <v>541647</v>
       </c>
       <c r="R16" t="n">
-        <v>6711610</v>
+        <v>6711571</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -6292,6 +6292,274 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123796614</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57857</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lerbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>541911</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6712029</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123800093</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97353</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kroken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>542086</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6712209</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Vid vägkant</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Åsa Weinberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123610047</v>
+        <v>123609153</v>
       </c>
       <c r="B15" t="n">
         <v>98396</v>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2439,14 +2439,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541721</v>
+        <v>541647</v>
       </c>
       <c r="R15" t="n">
-        <v>6711610</v>
+        <v>6711571</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2521,7 +2521,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123609153</v>
+        <v>123610047</v>
       </c>
       <c r="B16" t="n">
         <v>98396</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2573,14 +2573,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541647</v>
+        <v>541721</v>
       </c>
       <c r="R16" t="n">
-        <v>6711571</v>
+        <v>6711610</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4953,7 +4953,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123774773</v>
+        <v>123777220</v>
       </c>
       <c r="B34" t="n">
         <v>98396</v>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541703</v>
+        <v>541679</v>
       </c>
       <c r="R34" t="n">
-        <v>6711589</v>
+        <v>6711585</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5087,7 +5087,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123774473</v>
+        <v>123774773</v>
       </c>
       <c r="B35" t="n">
         <v>98396</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5139,17 +5139,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541738</v>
+        <v>541703</v>
       </c>
       <c r="R35" t="n">
-        <v>6711622</v>
+        <v>6711589</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5221,7 +5221,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123777220</v>
+        <v>123774473</v>
       </c>
       <c r="B36" t="n">
         <v>98396</v>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5273,17 +5273,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541679</v>
+        <v>541738</v>
       </c>
       <c r="R36" t="n">
-        <v>6711585</v>
+        <v>6711622</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -6560,6 +6560,566 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123831788</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>541839</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6711731</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123831817</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>541838</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6711732</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123831759</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>541837</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6711742</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123831066</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Kroken, Vika , Torvströmyran, Kroken, Vika , Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>541923</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6712001</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123830750</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>541959</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6712101</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517088</v>
+        <v>123518254</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,12 +823,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541805</v>
+        <v>541812</v>
       </c>
       <c r="R3" t="n">
-        <v>6711682</v>
+        <v>6711741</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123515231</v>
+        <v>123517161</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541812</v>
+        <v>541805</v>
       </c>
       <c r="R4" t="n">
-        <v>6711741</v>
+        <v>6711682</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,11 +1035,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517424</v>
+        <v>123515444</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1068,35 +1063,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541783</v>
+        <v>541772</v>
       </c>
       <c r="R5" t="n">
-        <v>6711682</v>
+        <v>6711742</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1139,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,7 +1152,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Röjning runt knärot</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,28 +1166,9 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1196,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123515352</v>
+        <v>123518065</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1287,7 +1276,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1297,12 +1286,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Yta 4x4 m</t>
+          <t>Invid en grov tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1335,10 +1324,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123515444</v>
+        <v>123515156</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>57643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,43 +1336,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1391,13 +1376,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541772</v>
+        <v>541812</v>
       </c>
       <c r="R7" t="n">
-        <v>6711742</v>
+        <v>6711741</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1426,7 +1411,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1436,12 +1421,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Röjning runt knärot</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1450,9 +1430,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1469,10 +1453,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123516472</v>
+        <v>123517424</v>
       </c>
       <c r="B8" t="n">
-        <v>58165</v>
+        <v>57506</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1481,20 +1465,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1507,7 +1491,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1517,13 +1501,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541809</v>
+        <v>541783</v>
       </c>
       <c r="R8" t="n">
-        <v>6711625</v>
+        <v>6711682</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1552,7 +1536,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1562,7 +1546,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,6 +1557,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1589,10 +1593,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123516006</v>
+        <v>123516472</v>
       </c>
       <c r="B9" t="n">
-        <v>57857</v>
+        <v>58168</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1605,16 +1609,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1622,20 +1626,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1645,13 +1641,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541818</v>
+        <v>541809</v>
       </c>
       <c r="R9" t="n">
-        <v>6711671</v>
+        <v>6711625</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1680,7 +1676,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1690,7 +1686,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1701,11 +1697,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1725,7 +1716,7 @@
         <v>123517700</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1856,10 +1847,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123515156</v>
+        <v>123515928</v>
       </c>
       <c r="B11" t="n">
-        <v>57640</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1868,39 +1859,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1908,13 +1903,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541812</v>
+        <v>541818</v>
       </c>
       <c r="R11" t="n">
-        <v>6711741</v>
+        <v>6711671</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1943,7 +1938,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1953,7 +1948,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1962,12 +1957,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1985,10 +1981,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123515928</v>
+        <v>123516006</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>57860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1997,43 +1993,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2076,7 +2072,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2086,7 +2082,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2095,13 +2091,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2119,10 +2114,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123609341</v>
+        <v>123606143</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2154,7 +2149,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2175,10 +2170,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541667</v>
+        <v>541691</v>
       </c>
       <c r="R13" t="n">
-        <v>6711554</v>
+        <v>6711610</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -2210,7 +2205,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2220,7 +2215,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2253,10 +2248,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123606143</v>
+        <v>123607946</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2288,7 +2283,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2309,10 +2304,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541691</v>
+        <v>541647</v>
       </c>
       <c r="R14" t="n">
-        <v>6711610</v>
+        <v>6711571</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2344,7 +2339,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2354,7 +2349,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2387,10 +2382,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123609153</v>
+        <v>123609282</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2422,7 +2417,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2443,10 +2438,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541647</v>
+        <v>541667</v>
       </c>
       <c r="R15" t="n">
-        <v>6711571</v>
+        <v>6711554</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2478,7 +2473,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2488,7 +2483,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2521,10 +2516,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123610047</v>
+        <v>123610005</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2556,12 +2551,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2612,7 +2607,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2622,7 +2617,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2658,7 +2653,7 @@
         <v>123609837</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2789,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123775574</v>
+        <v>123774836</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2824,7 +2819,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2841,14 +2836,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541671</v>
+        <v>541703</v>
       </c>
       <c r="R18" t="n">
-        <v>6711571</v>
+        <v>6711589</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2880,7 +2875,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2890,7 +2885,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2923,10 +2918,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123776010</v>
+        <v>123772375</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2958,7 +2953,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2975,17 +2970,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541669</v>
+        <v>541819</v>
       </c>
       <c r="R19" t="n">
-        <v>6711539</v>
+        <v>6711662</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3014,7 +3009,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3024,7 +3019,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3057,10 +3052,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123780468</v>
+        <v>123775574</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3092,12 +3087,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3109,14 +3104,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541805</v>
+        <v>541671</v>
       </c>
       <c r="R20" t="n">
-        <v>6711708</v>
+        <v>6711571</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -3148,7 +3143,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3158,12 +3153,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Alldeles invid körspår.</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3196,10 +3186,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123779653</v>
+        <v>123776982</v>
       </c>
       <c r="B21" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3208,30 +3198,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3248,17 +3238,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541788</v>
+        <v>541650</v>
       </c>
       <c r="R21" t="n">
-        <v>6711796</v>
+        <v>6711541</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3287,7 +3277,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3297,7 +3287,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3330,10 +3320,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123775610</v>
+        <v>123777114</v>
       </c>
       <c r="B22" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3365,7 +3355,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3382,14 +3372,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541674</v>
+        <v>541658</v>
       </c>
       <c r="R22" t="n">
-        <v>6711552</v>
+        <v>6711551</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3421,7 +3411,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3431,7 +3421,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3464,10 +3454,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123776982</v>
+        <v>123775610</v>
       </c>
       <c r="B23" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3499,7 +3489,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3516,14 +3506,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541650</v>
+        <v>541674</v>
       </c>
       <c r="R23" t="n">
-        <v>6711541</v>
+        <v>6711552</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3555,7 +3545,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3565,7 +3555,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3598,10 +3588,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123778741</v>
+        <v>123772073</v>
       </c>
       <c r="B24" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3610,30 +3600,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3643,7 +3633,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3654,10 +3644,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541760</v>
+        <v>541829</v>
       </c>
       <c r="R24" t="n">
-        <v>6711731</v>
+        <v>6711695</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3689,7 +3679,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3699,7 +3689,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3732,10 +3722,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123776928</v>
+        <v>123779653</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3744,30 +3734,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3784,17 +3774,17 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541657</v>
+        <v>541788</v>
       </c>
       <c r="R25" t="n">
-        <v>6711519</v>
+        <v>6711796</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3823,7 +3813,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3833,7 +3823,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3866,10 +3856,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123777859</v>
+        <v>123779278</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3878,30 +3868,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3911,7 +3901,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3922,13 +3912,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541727</v>
+        <v>541778</v>
       </c>
       <c r="R26" t="n">
-        <v>6711663</v>
+        <v>6711781</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3957,7 +3947,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3967,7 +3957,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Invid en  utgrävd bäck</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3982,7 +3977,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4000,10 +3995,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123772073</v>
+        <v>123778741</v>
       </c>
       <c r="B27" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4012,30 +4007,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4045,7 +4040,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -4056,10 +4051,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541829</v>
+        <v>541760</v>
       </c>
       <c r="R27" t="n">
-        <v>6711695</v>
+        <v>6711731</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -4091,7 +4086,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4101,7 +4096,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4134,10 +4129,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123777970</v>
+        <v>123775826</v>
       </c>
       <c r="B28" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4169,7 +4164,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4186,17 +4181,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541726</v>
+        <v>541668</v>
       </c>
       <c r="R28" t="n">
-        <v>6711685</v>
+        <v>6711539</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4225,7 +4220,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4235,7 +4230,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4268,10 +4263,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123778521</v>
+        <v>123780468</v>
       </c>
       <c r="B29" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4280,35 +4275,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4324,13 +4319,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541722</v>
+        <v>541805</v>
       </c>
       <c r="R29" t="n">
-        <v>6711715</v>
+        <v>6711708</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4359,7 +4354,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4369,12 +4364,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Alldeles invid en gammal grov gran. Ca 4 meter från bäck.</t>
+          <t>Alldeles invid körspår.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4389,7 +4384,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4407,10 +4402,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123771872</v>
+        <v>123777793</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4442,7 +4437,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4463,13 +4458,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541839</v>
+        <v>541741</v>
       </c>
       <c r="R30" t="n">
-        <v>6711709</v>
+        <v>6711669</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4498,7 +4493,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4508,7 +4503,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4541,10 +4536,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123779278</v>
+        <v>123776010</v>
       </c>
       <c r="B31" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4553,30 +4548,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4586,24 +4581,24 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541778</v>
+        <v>541669</v>
       </c>
       <c r="R31" t="n">
-        <v>6711781</v>
+        <v>6711539</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4632,7 +4627,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4642,12 +4637,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Invid en  utgrävd bäck</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4662,7 +4652,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4680,10 +4670,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123772375</v>
+        <v>123780218</v>
       </c>
       <c r="B32" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4713,14 +4703,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4736,13 +4722,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541819</v>
+        <v>541787</v>
       </c>
       <c r="R32" t="n">
-        <v>6711662</v>
+        <v>6711764</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4771,7 +4757,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4781,7 +4767,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4814,10 +4800,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123778290</v>
+        <v>123772762</v>
       </c>
       <c r="B33" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4826,35 +4812,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4870,13 +4856,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541709</v>
+        <v>541824</v>
       </c>
       <c r="R33" t="n">
-        <v>6711698</v>
+        <v>6711621</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4905,7 +4891,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4915,12 +4901,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I närheten av grävt dike alternativt utgrävd bäck.</t>
+          <t>Vackert melerade blad</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4935,7 +4921,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4956,7 +4942,7 @@
         <v>123777220</v>
       </c>
       <c r="B34" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5087,10 +5073,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123774773</v>
+        <v>123772523</v>
       </c>
       <c r="B35" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5122,7 +5108,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5139,17 +5125,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541703</v>
+        <v>541828</v>
       </c>
       <c r="R35" t="n">
-        <v>6711589</v>
+        <v>6711635</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5178,7 +5164,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5188,7 +5174,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5224,7 +5210,7 @@
         <v>123774473</v>
       </c>
       <c r="B36" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5355,10 +5341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123780218</v>
+        <v>123776928</v>
       </c>
       <c r="B37" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5388,10 +5374,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5403,14 +5393,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541787</v>
+        <v>541657</v>
       </c>
       <c r="R37" t="n">
-        <v>6711764</v>
+        <v>6711519</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -5442,7 +5432,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5452,7 +5442,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5485,10 +5475,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123775826</v>
+        <v>123778010</v>
       </c>
       <c r="B38" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5520,7 +5510,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5537,17 +5527,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541668</v>
+        <v>541726</v>
       </c>
       <c r="R38" t="n">
-        <v>6711539</v>
+        <v>6711685</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5576,7 +5566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5586,7 +5576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5619,10 +5609,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123772523</v>
+        <v>123778521</v>
       </c>
       <c r="B39" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5631,35 +5621,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5671,17 +5661,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Torvströmyren, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541828</v>
+        <v>541722</v>
       </c>
       <c r="R39" t="n">
-        <v>6711635</v>
+        <v>6711715</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5710,7 +5700,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5720,7 +5710,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Alldeles invid en gammal grov gran. Ca 4 meter från bäck.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5735,7 +5730,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5753,10 +5748,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123777114</v>
+        <v>123777859</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5788,7 +5783,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5805,17 +5800,17 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541658</v>
+        <v>541727</v>
       </c>
       <c r="R40" t="n">
-        <v>6711551</v>
+        <v>6711663</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5844,7 +5839,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5854,7 +5849,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5887,10 +5882,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123780300</v>
+        <v>123771872</v>
       </c>
       <c r="B41" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5922,7 +5917,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5939,17 +5934,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Torvströmyran, Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541783</v>
+        <v>541839</v>
       </c>
       <c r="R41" t="n">
-        <v>6711759</v>
+        <v>6711709</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5978,7 +5973,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5988,7 +5983,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6021,10 +6016,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123772762</v>
+        <v>123778290</v>
       </c>
       <c r="B42" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6033,35 +6028,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6077,13 +6072,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541824</v>
+        <v>541709</v>
       </c>
       <c r="R42" t="n">
-        <v>6711621</v>
+        <v>6711698</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6112,7 +6107,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6122,12 +6117,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Vackert melerade blad</t>
+          <t>I närheten av grävt dike alternativt utgrävd bäck.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6142,7 +6137,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6160,10 +6155,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123777793</v>
+        <v>123780300</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6195,7 +6190,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6212,14 +6207,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541741</v>
+        <v>541783</v>
       </c>
       <c r="R43" t="n">
-        <v>6711669</v>
+        <v>6711759</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -6251,7 +6246,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6261,7 +6256,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6294,10 +6289,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123796614</v>
+        <v>123800093</v>
       </c>
       <c r="B44" t="n">
-        <v>57857</v>
+        <v>97370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6310,49 +6305,53 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541911</v>
+        <v>542086</v>
       </c>
       <c r="R44" t="n">
-        <v>6712029</v>
+        <v>6712209</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6381,7 +6380,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6391,7 +6390,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Vid vägkant</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6400,6 +6404,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6423,10 +6428,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123800093</v>
+        <v>123796614</v>
       </c>
       <c r="B45" t="n">
-        <v>97353</v>
+        <v>57860</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6439,53 +6444,49 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542086</v>
+        <v>541911</v>
       </c>
       <c r="R45" t="n">
-        <v>6712209</v>
+        <v>6712029</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6514,7 +6515,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6524,12 +6525,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Vid vägkant</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6538,7 +6534,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6562,7 +6557,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123831788</v>
+        <v>123831817</v>
       </c>
       <c r="B46" t="n">
         <v>98502</v>
@@ -6602,10 +6597,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541839</v>
+        <v>541838</v>
       </c>
       <c r="R46" t="n">
-        <v>6711731</v>
+        <v>6711732</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6637,7 +6632,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6647,7 +6642,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6674,7 +6669,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123831817</v>
+        <v>123831788</v>
       </c>
       <c r="B47" t="n">
         <v>98502</v>
@@ -6714,10 +6709,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541838</v>
+        <v>541839</v>
       </c>
       <c r="R47" t="n">
-        <v>6711732</v>
+        <v>6711731</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6749,7 +6744,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6759,7 +6754,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123518254</v>
+        <v>123515231</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,12 +823,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517161</v>
+        <v>123517887</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541805</v>
+        <v>541792</v>
       </c>
       <c r="R4" t="n">
-        <v>6711682</v>
+        <v>6711744</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,6 +1035,11 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1051,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123515444</v>
+        <v>123517088</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1107,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541772</v>
+        <v>541805</v>
       </c>
       <c r="R5" t="n">
-        <v>6711742</v>
+        <v>6711682</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1142,7 +1147,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,12 +1157,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Röjning runt knärot</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,6 +1169,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1185,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123518065</v>
+        <v>123516006</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,43 +1202,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1241,10 +1246,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541792</v>
+        <v>541818</v>
       </c>
       <c r="R6" t="n">
-        <v>6711744</v>
+        <v>6711671</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1276,7 +1281,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1286,12 +1291,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Invid en grov tall.</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1324,10 +1323,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123515156</v>
+        <v>123515928</v>
       </c>
       <c r="B7" t="n">
-        <v>57643</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,39 +1335,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1376,13 +1379,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541812</v>
+        <v>541818</v>
       </c>
       <c r="R7" t="n">
-        <v>6711741</v>
+        <v>6711671</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1411,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1421,7 +1424,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,12 +1433,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1453,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123517424</v>
+        <v>123516472</v>
       </c>
       <c r="B8" t="n">
-        <v>57506</v>
+        <v>58169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1465,20 +1469,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1491,7 +1495,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1501,13 +1505,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541783</v>
+        <v>541809</v>
       </c>
       <c r="R8" t="n">
-        <v>6711682</v>
+        <v>6711625</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1536,7 +1540,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1546,7 +1550,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1557,26 +1561,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1593,10 +1577,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123516472</v>
+        <v>123515444</v>
       </c>
       <c r="B9" t="n">
-        <v>58168</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1605,35 +1589,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1641,13 +1633,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541809</v>
+        <v>541772</v>
       </c>
       <c r="R9" t="n">
-        <v>6711625</v>
+        <v>6711742</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1676,7 +1668,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1686,7 +1678,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Röjning runt knärot</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1695,6 +1692,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1713,10 +1711,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123517700</v>
+        <v>123515156</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>57644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1725,43 +1723,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1769,13 +1763,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541783</v>
+        <v>541812</v>
       </c>
       <c r="R10" t="n">
-        <v>6711682</v>
+        <v>6711741</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1804,7 +1798,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1808,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1823,7 +1817,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1847,10 +1840,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123515928</v>
+        <v>123517424</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1859,43 +1852,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1903,10 +1888,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541818</v>
+        <v>541783</v>
       </c>
       <c r="R11" t="n">
-        <v>6711671</v>
+        <v>6711682</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1938,7 +1923,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1948,7 +1933,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1957,13 +1942,27 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1981,10 +1980,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123516006</v>
+        <v>123517700</v>
       </c>
       <c r="B12" t="n">
-        <v>57860</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1993,43 +1992,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2037,10 +2036,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541818</v>
+        <v>541783</v>
       </c>
       <c r="R12" t="n">
-        <v>6711671</v>
+        <v>6711682</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
@@ -2072,7 +2071,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2082,7 +2081,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2091,6 +2090,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2114,10 +2114,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123606143</v>
+        <v>123605902</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123607946</v>
+        <v>123609341</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541647</v>
+        <v>541667</v>
       </c>
       <c r="R14" t="n">
-        <v>6711571</v>
+        <v>6711554</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2382,10 +2382,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123609282</v>
+        <v>123609210</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541667</v>
+        <v>541647</v>
       </c>
       <c r="R15" t="n">
-        <v>6711554</v>
+        <v>6711571</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123610005</v>
+        <v>123610047</v>
       </c>
       <c r="B16" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2653,7 +2653,7 @@
         <v>123609837</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123774836</v>
+        <v>123776928</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541703</v>
+        <v>541657</v>
       </c>
       <c r="R18" t="n">
-        <v>6711589</v>
+        <v>6711519</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2918,10 +2918,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123772375</v>
+        <v>123775826</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2970,17 +2970,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541819</v>
+        <v>541668</v>
       </c>
       <c r="R19" t="n">
-        <v>6711662</v>
+        <v>6711539</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3052,10 +3052,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123775574</v>
+        <v>123778290</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>100682</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3064,35 +3064,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3104,17 +3104,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541671</v>
+        <v>541709</v>
       </c>
       <c r="R20" t="n">
-        <v>6711571</v>
+        <v>6711698</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3153,7 +3153,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I närheten av grävt dike alternativt utgrävd bäck.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3168,7 +3173,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3186,10 +3191,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123776982</v>
+        <v>123780468</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3221,12 +3226,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3238,14 +3243,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541650</v>
+        <v>541805</v>
       </c>
       <c r="R21" t="n">
-        <v>6711541</v>
+        <v>6711708</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3277,7 +3282,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3287,7 +3292,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Alldeles invid körspår.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3320,10 +3330,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123777114</v>
+        <v>123772200</v>
       </c>
       <c r="B22" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3355,7 +3365,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3368,18 +3378,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541658</v>
+        <v>541829</v>
       </c>
       <c r="R22" t="n">
-        <v>6711551</v>
+        <v>6711695</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3411,7 +3419,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3421,7 +3429,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3430,7 +3438,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3454,10 +3461,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123775610</v>
+        <v>123774836</v>
       </c>
       <c r="B23" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3489,7 +3496,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3506,14 +3513,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541674</v>
+        <v>541703</v>
       </c>
       <c r="R23" t="n">
-        <v>6711552</v>
+        <v>6711589</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3545,7 +3552,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3555,7 +3562,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3588,10 +3595,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123772073</v>
+        <v>123771872</v>
       </c>
       <c r="B24" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3623,7 +3630,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3644,13 +3651,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541829</v>
+        <v>541839</v>
       </c>
       <c r="R24" t="n">
-        <v>6711695</v>
+        <v>6711709</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3679,7 +3686,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3689,7 +3696,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3722,10 +3729,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123779653</v>
+        <v>123777970</v>
       </c>
       <c r="B25" t="n">
-        <v>100680</v>
+        <v>98504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3734,30 +3741,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3778,13 +3785,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541788</v>
+        <v>541726</v>
       </c>
       <c r="R25" t="n">
-        <v>6711796</v>
+        <v>6711685</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3813,7 +3820,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3823,7 +3830,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3856,10 +3863,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123779278</v>
+        <v>123775610</v>
       </c>
       <c r="B26" t="n">
-        <v>100680</v>
+        <v>98504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3868,30 +3875,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3901,24 +3908,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541778</v>
+        <v>541674</v>
       </c>
       <c r="R26" t="n">
-        <v>6711781</v>
+        <v>6711552</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3947,7 +3954,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3957,12 +3964,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Invid en  utgrävd bäck</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3977,7 +3979,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3995,10 +3997,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123778741</v>
+        <v>123774473</v>
       </c>
       <c r="B27" t="n">
-        <v>100680</v>
+        <v>98504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4007,30 +4009,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4040,7 +4042,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -4051,13 +4053,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541760</v>
+        <v>541738</v>
       </c>
       <c r="R27" t="n">
-        <v>6711731</v>
+        <v>6711622</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4086,7 +4088,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4096,7 +4098,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4129,10 +4131,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123775826</v>
+        <v>123776010</v>
       </c>
       <c r="B28" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4164,7 +4166,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4185,13 +4187,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541668</v>
+        <v>541669</v>
       </c>
       <c r="R28" t="n">
         <v>6711539</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4220,7 +4222,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4230,7 +4232,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4263,10 +4265,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123780468</v>
+        <v>123776982</v>
       </c>
       <c r="B29" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4298,12 +4300,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4315,14 +4317,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541805</v>
+        <v>541650</v>
       </c>
       <c r="R29" t="n">
-        <v>6711708</v>
+        <v>6711541</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4354,7 +4356,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4364,12 +4366,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Alldeles invid körspår.</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4402,10 +4399,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123777793</v>
+        <v>123777114</v>
       </c>
       <c r="B30" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4437,7 +4434,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4454,14 +4451,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541741</v>
+        <v>541658</v>
       </c>
       <c r="R30" t="n">
-        <v>6711669</v>
+        <v>6711551</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4493,7 +4490,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4503,7 +4500,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4536,10 +4533,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123776010</v>
+        <v>123777793</v>
       </c>
       <c r="B31" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4571,7 +4568,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4588,14 +4585,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541669</v>
+        <v>541741</v>
       </c>
       <c r="R31" t="n">
-        <v>6711539</v>
+        <v>6711669</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4627,7 +4624,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4637,7 +4634,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4670,10 +4667,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123780218</v>
+        <v>123772762</v>
       </c>
       <c r="B32" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4703,10 +4700,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4722,10 +4723,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541787</v>
+        <v>541824</v>
       </c>
       <c r="R32" t="n">
-        <v>6711764</v>
+        <v>6711621</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4757,7 +4758,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4767,7 +4768,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Vackert melerade blad</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4800,10 +4806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123772762</v>
+        <v>123777859</v>
       </c>
       <c r="B33" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4835,7 +4841,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4856,13 +4862,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541824</v>
+        <v>541727</v>
       </c>
       <c r="R33" t="n">
-        <v>6711621</v>
+        <v>6711663</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4891,7 +4897,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4901,12 +4907,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Vackert melerade blad</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4939,10 +4940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123777220</v>
+        <v>123780218</v>
       </c>
       <c r="B34" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4972,14 +4973,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4991,14 +4988,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541679</v>
+        <v>541787</v>
       </c>
       <c r="R34" t="n">
-        <v>6711585</v>
+        <v>6711764</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -5030,7 +5027,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5040,7 +5037,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5073,10 +5070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123772523</v>
+        <v>123778521</v>
       </c>
       <c r="B35" t="n">
-        <v>98502</v>
+        <v>100682</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5085,35 +5082,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5125,17 +5122,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Torvströmyren, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541828</v>
+        <v>541722</v>
       </c>
       <c r="R35" t="n">
-        <v>6711635</v>
+        <v>6711715</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5164,7 +5161,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5174,7 +5171,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Alldeles invid en gammal grov gran. Ca 4 meter från bäck.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5189,7 +5191,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5207,10 +5209,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123774473</v>
+        <v>123779653</v>
       </c>
       <c r="B36" t="n">
-        <v>98502</v>
+        <v>100682</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5219,30 +5221,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5263,13 +5265,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541738</v>
+        <v>541788</v>
       </c>
       <c r="R36" t="n">
-        <v>6711622</v>
+        <v>6711796</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5298,7 +5300,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5308,7 +5310,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5341,10 +5343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123776928</v>
+        <v>123772523</v>
       </c>
       <c r="B37" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5376,7 +5378,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5393,17 +5395,17 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541657</v>
+        <v>541828</v>
       </c>
       <c r="R37" t="n">
-        <v>6711519</v>
+        <v>6711635</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5432,7 +5434,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5442,7 +5444,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5475,10 +5477,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123778010</v>
+        <v>123775574</v>
       </c>
       <c r="B38" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5527,14 +5529,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541726</v>
+        <v>541671</v>
       </c>
       <c r="R38" t="n">
-        <v>6711685</v>
+        <v>6711571</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5566,7 +5568,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5576,7 +5578,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5609,10 +5611,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123778521</v>
+        <v>123777220</v>
       </c>
       <c r="B39" t="n">
-        <v>100680</v>
+        <v>98504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5621,35 +5623,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5661,17 +5663,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541722</v>
+        <v>541679</v>
       </c>
       <c r="R39" t="n">
-        <v>6711715</v>
+        <v>6711585</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5700,7 +5702,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5710,12 +5712,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Alldeles invid en gammal grov gran. Ca 4 meter från bäck.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5730,7 +5727,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5748,10 +5745,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123777859</v>
+        <v>123779278</v>
       </c>
       <c r="B40" t="n">
-        <v>98502</v>
+        <v>100682</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5760,30 +5757,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5793,7 +5790,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5804,13 +5801,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541727</v>
+        <v>541778</v>
       </c>
       <c r="R40" t="n">
-        <v>6711663</v>
+        <v>6711781</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5839,7 +5836,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5849,7 +5846,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Invid en  utgrävd bäck</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5864,7 +5866,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5882,10 +5884,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123771872</v>
+        <v>123780300</v>
       </c>
       <c r="B41" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5917,7 +5919,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5934,17 +5936,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541839</v>
+        <v>541783</v>
       </c>
       <c r="R41" t="n">
-        <v>6711709</v>
+        <v>6711759</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5973,7 +5975,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5983,7 +5985,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6016,10 +6018,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123778290</v>
+        <v>123772375</v>
       </c>
       <c r="B42" t="n">
-        <v>100680</v>
+        <v>98504</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6028,35 +6030,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6072,10 +6074,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541709</v>
+        <v>541819</v>
       </c>
       <c r="R42" t="n">
-        <v>6711698</v>
+        <v>6711662</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -6107,7 +6109,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6117,12 +6119,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>I närheten av grävt dike alternativt utgrävd bäck.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6137,7 +6134,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6155,10 +6152,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123780300</v>
+        <v>123778741</v>
       </c>
       <c r="B43" t="n">
-        <v>98502</v>
+        <v>100682</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6167,30 +6164,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6200,21 +6197,21 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Torvströmyran, Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541783</v>
+        <v>541760</v>
       </c>
       <c r="R43" t="n">
-        <v>6711759</v>
+        <v>6711731</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -6246,7 +6243,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6256,7 +6253,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6289,10 +6286,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123800093</v>
+        <v>123796614</v>
       </c>
       <c r="B44" t="n">
-        <v>97370</v>
+        <v>57861</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6305,53 +6302,49 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542086</v>
+        <v>541911</v>
       </c>
       <c r="R44" t="n">
-        <v>6712209</v>
+        <v>6712029</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6380,7 +6373,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6390,12 +6383,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Vid vägkant</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6404,7 +6392,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6428,10 +6415,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123796614</v>
+        <v>123800093</v>
       </c>
       <c r="B45" t="n">
-        <v>57860</v>
+        <v>97372</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6444,49 +6431,53 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541911</v>
+        <v>542086</v>
       </c>
       <c r="R45" t="n">
-        <v>6712029</v>
+        <v>6712209</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6515,7 +6506,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6525,7 +6516,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Vid vägkant</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6534,6 +6530,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6557,10 +6554,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123831817</v>
+        <v>123831759</v>
       </c>
       <c r="B46" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6597,10 +6594,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541838</v>
+        <v>541837</v>
       </c>
       <c r="R46" t="n">
-        <v>6711732</v>
+        <v>6711742</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6632,7 +6629,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6642,7 +6639,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6669,10 +6666,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123831788</v>
+        <v>123831817</v>
       </c>
       <c r="B47" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6709,10 +6706,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541839</v>
+        <v>541838</v>
       </c>
       <c r="R47" t="n">
-        <v>6711731</v>
+        <v>6711732</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6744,7 +6741,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6754,7 +6751,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6781,10 +6778,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123831759</v>
+        <v>123830750</v>
       </c>
       <c r="B48" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6817,14 +6814,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541837</v>
+        <v>541959</v>
       </c>
       <c r="R48" t="n">
-        <v>6711742</v>
+        <v>6712101</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6856,7 +6853,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6866,7 +6863,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6896,7 +6893,7 @@
         <v>123831066</v>
       </c>
       <c r="B49" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7005,10 +7002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123830750</v>
+        <v>123831788</v>
       </c>
       <c r="B50" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7041,14 +7038,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541959</v>
+        <v>541839</v>
       </c>
       <c r="R50" t="n">
-        <v>6712101</v>
+        <v>6711731</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -7080,7 +7077,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7090,7 +7087,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -3997,7 +3997,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123774473</v>
+        <v>123776010</v>
       </c>
       <c r="B27" t="n">
         <v>98504</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4049,17 +4049,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541738</v>
+        <v>541669</v>
       </c>
       <c r="R27" t="n">
-        <v>6711622</v>
+        <v>6711539</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4131,7 +4131,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123776010</v>
+        <v>123776982</v>
       </c>
       <c r="B28" t="n">
         <v>98504</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541669</v>
+        <v>541650</v>
       </c>
       <c r="R28" t="n">
-        <v>6711539</v>
+        <v>6711541</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4265,7 +4265,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123776982</v>
+        <v>123774473</v>
       </c>
       <c r="B29" t="n">
         <v>98504</v>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4317,17 +4317,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541650</v>
+        <v>541738</v>
       </c>
       <c r="R29" t="n">
-        <v>6711541</v>
+        <v>6711622</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -2913,7 +2913,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123777859</v>
+        <v>123777114</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2965,17 +2965,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541727</v>
+        <v>541658</v>
       </c>
       <c r="R19" t="n">
-        <v>6711663</v>
+        <v>6711551</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123779653</v>
+        <v>123775574</v>
       </c>
       <c r="B20" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3059,30 +3059,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3099,17 +3099,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541788</v>
+        <v>541671</v>
       </c>
       <c r="R20" t="n">
-        <v>6711796</v>
+        <v>6711571</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123779278</v>
+        <v>123777220</v>
       </c>
       <c r="B21" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3193,30 +3193,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541778</v>
+        <v>541679</v>
       </c>
       <c r="R21" t="n">
-        <v>6711781</v>
+        <v>6711585</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3282,12 +3282,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Invid en  utgrävd bäck</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3302,7 +3297,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3320,10 +3315,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123778290</v>
+        <v>123777970</v>
       </c>
       <c r="B22" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3332,35 +3327,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3376,13 +3371,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541709</v>
+        <v>541726</v>
       </c>
       <c r="R22" t="n">
-        <v>6711698</v>
+        <v>6711685</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3411,7 +3406,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3421,12 +3416,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I närheten av grävt dike alternativt utgrävd bäck.</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3441,7 +3431,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3459,7 +3449,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123772375</v>
+        <v>123777793</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3494,7 +3484,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3515,13 +3505,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541819</v>
+        <v>541741</v>
       </c>
       <c r="R23" t="n">
-        <v>6711662</v>
+        <v>6711669</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3550,7 +3540,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3560,7 +3550,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3593,7 +3583,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123774836</v>
+        <v>123780300</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3628,7 +3618,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3645,14 +3635,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541703</v>
+        <v>541783</v>
       </c>
       <c r="R24" t="n">
-        <v>6711589</v>
+        <v>6711759</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3684,7 +3674,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3694,7 +3684,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3727,7 +3717,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123774566</v>
+        <v>123774473</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3762,7 +3752,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3818,7 +3808,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3828,7 +3818,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3861,7 +3851,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123772073</v>
+        <v>123780468</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3901,7 +3891,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3917,10 +3907,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541829</v>
+        <v>541805</v>
       </c>
       <c r="R26" t="n">
-        <v>6711695</v>
+        <v>6711708</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3952,7 +3942,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3962,7 +3952,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Alldeles invid körspår.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3995,7 +3990,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123772762</v>
+        <v>123776010</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -4030,7 +4025,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4047,14 +4042,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541824</v>
+        <v>541669</v>
       </c>
       <c r="R27" t="n">
-        <v>6711621</v>
+        <v>6711539</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -4086,7 +4081,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4096,12 +4091,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Vackert melerade blad</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4134,7 +4124,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123777220</v>
+        <v>123772523</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -4169,7 +4159,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4186,17 +4176,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541679</v>
+        <v>541828</v>
       </c>
       <c r="R28" t="n">
-        <v>6711585</v>
+        <v>6711635</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4225,7 +4215,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4235,7 +4225,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4268,7 +4258,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123780519</v>
+        <v>123774836</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -4303,7 +4293,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4320,14 +4310,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Torvströmyran, Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541805</v>
+        <v>541703</v>
       </c>
       <c r="R29" t="n">
-        <v>6711708</v>
+        <v>6711589</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4359,7 +4349,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4369,7 +4359,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4402,10 +4392,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123775574</v>
+        <v>123778741</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4414,30 +4404,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4447,21 +4437,21 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541671</v>
+        <v>541760</v>
       </c>
       <c r="R30" t="n">
-        <v>6711571</v>
+        <v>6711731</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4493,7 +4483,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4503,7 +4493,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4536,7 +4526,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123775610</v>
+        <v>123776982</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4571,7 +4561,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4588,14 +4578,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541674</v>
+        <v>541650</v>
       </c>
       <c r="R31" t="n">
-        <v>6711552</v>
+        <v>6711541</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4627,7 +4617,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4637,7 +4627,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4670,7 +4660,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123777793</v>
+        <v>123775826</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4705,7 +4695,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4722,17 +4712,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541741</v>
+        <v>541668</v>
       </c>
       <c r="R32" t="n">
-        <v>6711669</v>
+        <v>6711539</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4761,7 +4751,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4771,7 +4761,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4804,10 +4794,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123776010</v>
+        <v>123778521</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4816,35 +4806,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4856,17 +4846,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541669</v>
+        <v>541722</v>
       </c>
       <c r="R33" t="n">
-        <v>6711539</v>
+        <v>6711715</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4895,7 +4885,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4905,7 +4895,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Alldeles invid en gammal grov gran. Ca 4 meter från bäck.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4920,7 +4915,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4938,10 +4933,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123780300</v>
+        <v>123779653</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4950,30 +4945,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4990,17 +4985,17 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Torvströmyran, Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541783</v>
+        <v>541788</v>
       </c>
       <c r="R34" t="n">
-        <v>6711759</v>
+        <v>6711796</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5029,7 +5024,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5039,7 +5034,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5072,7 +5067,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123776928</v>
+        <v>123777859</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -5107,7 +5102,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5124,17 +5119,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541657</v>
+        <v>541727</v>
       </c>
       <c r="R35" t="n">
-        <v>6711519</v>
+        <v>6711663</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5163,7 +5158,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5173,7 +5168,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5206,7 +5201,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123778010</v>
+        <v>123772073</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -5241,7 +5236,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5262,10 +5257,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541726</v>
+        <v>541829</v>
       </c>
       <c r="R36" t="n">
-        <v>6711685</v>
+        <v>6711695</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -5297,7 +5292,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5307,7 +5302,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5340,7 +5335,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123772523</v>
+        <v>123776928</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -5375,7 +5370,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5392,17 +5387,17 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Torvströmyren, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541828</v>
+        <v>541657</v>
       </c>
       <c r="R37" t="n">
-        <v>6711635</v>
+        <v>6711519</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5431,7 +5426,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5441,7 +5436,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5474,10 +5469,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123778741</v>
+        <v>123772375</v>
       </c>
       <c r="B38" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5486,30 +5481,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5519,7 +5514,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5530,13 +5525,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541760</v>
+        <v>541819</v>
       </c>
       <c r="R38" t="n">
-        <v>6711731</v>
+        <v>6711662</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5565,7 +5560,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5575,7 +5570,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5608,7 +5603,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123777114</v>
+        <v>123780218</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -5641,14 +5636,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5660,14 +5651,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541658</v>
+        <v>541787</v>
       </c>
       <c r="R39" t="n">
-        <v>6711551</v>
+        <v>6711764</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5699,7 +5690,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5709,7 +5700,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5742,7 +5733,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123776982</v>
+        <v>123772762</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -5777,7 +5768,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5794,14 +5785,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541650</v>
+        <v>541824</v>
       </c>
       <c r="R40" t="n">
-        <v>6711541</v>
+        <v>6711621</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5833,7 +5824,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5843,7 +5834,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Vackert melerade blad</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5876,10 +5872,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123777640</v>
+        <v>123778290</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5888,35 +5884,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5928,17 +5924,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541722</v>
+        <v>541709</v>
       </c>
       <c r="R41" t="n">
-        <v>6711656</v>
+        <v>6711698</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5967,7 +5963,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5977,7 +5973,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I närheten av grävt dike alternativt utgrävd bäck.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5992,7 +5993,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6010,7 +6011,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123771872</v>
+        <v>123775610</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -6045,7 +6046,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6062,17 +6063,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Torvströmyran, Dlr</t>
+          <t>Lerbäcken, Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541839</v>
+        <v>541674</v>
       </c>
       <c r="R42" t="n">
-        <v>6711709</v>
+        <v>6711552</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6101,7 +6102,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6111,7 +6112,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6144,7 +6145,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123775826</v>
+        <v>123777640</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -6179,7 +6180,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6200,13 +6201,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541668</v>
+        <v>541722</v>
       </c>
       <c r="R43" t="n">
-        <v>6711539</v>
+        <v>6711656</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6235,7 +6236,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6245,7 +6246,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6278,10 +6279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123778521</v>
+        <v>123771872</v>
       </c>
       <c r="B44" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6290,35 +6291,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -6334,10 +6335,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541722</v>
+        <v>541839</v>
       </c>
       <c r="R44" t="n">
-        <v>6711715</v>
+        <v>6711709</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -6369,7 +6370,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6379,12 +6380,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Alldeles invid en gammal grov gran. Ca 4 meter från bäck.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6399,7 +6395,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6417,10 +6413,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123780218</v>
+        <v>123779278</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6429,36 +6425,40 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541787</v>
+        <v>541778</v>
       </c>
       <c r="R45" t="n">
-        <v>6711764</v>
+        <v>6711781</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6514,7 +6514,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Invid en  utgrävd bäck</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6529,7 +6534,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6547,10 +6552,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123796614</v>
+        <v>123800093</v>
       </c>
       <c r="B46" t="n">
-        <v>57883</v>
+        <v>96982</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6563,49 +6568,53 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541911</v>
+        <v>542086</v>
       </c>
       <c r="R46" t="n">
-        <v>6712029</v>
+        <v>6712209</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6634,7 +6643,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6644,7 +6653,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Vid vägkant</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6653,6 +6667,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6676,10 +6691,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123800093</v>
+        <v>123796614</v>
       </c>
       <c r="B47" t="n">
-        <v>96982</v>
+        <v>57883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6692,53 +6707,49 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542086</v>
+        <v>541911</v>
       </c>
       <c r="R47" t="n">
-        <v>6712209</v>
+        <v>6712029</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6767,7 +6778,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6777,12 +6788,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Vid vägkant</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6791,7 +6797,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6815,7 +6820,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123831759</v>
+        <v>123830750</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6851,14 +6856,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541837</v>
+        <v>541959</v>
       </c>
       <c r="R48" t="n">
-        <v>6711742</v>
+        <v>6712101</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6890,7 +6895,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6900,7 +6905,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6927,7 +6932,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123831788</v>
+        <v>123831759</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6967,10 +6972,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541839</v>
+        <v>541837</v>
       </c>
       <c r="R49" t="n">
-        <v>6711731</v>
+        <v>6711742</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -7002,7 +7007,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7012,7 +7017,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7151,7 +7156,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123830750</v>
+        <v>123831788</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7187,14 +7192,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541959</v>
+        <v>541839</v>
       </c>
       <c r="R51" t="n">
-        <v>6712101</v>
+        <v>6711731</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7226,7 +7231,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7236,7 +7241,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -6552,10 +6552,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123800093</v>
+        <v>123796614</v>
       </c>
       <c r="B46" t="n">
-        <v>96982</v>
+        <v>57883</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6568,53 +6568,49 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroken, Dlr</t>
+          <t>Lerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542086</v>
+        <v>541911</v>
       </c>
       <c r="R46" t="n">
-        <v>6712209</v>
+        <v>6712029</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6643,7 +6639,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6653,12 +6649,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Vid vägkant</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6667,7 +6658,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6691,10 +6681,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123796614</v>
+        <v>123800093</v>
       </c>
       <c r="B47" t="n">
-        <v>57883</v>
+        <v>96982</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6707,49 +6697,53 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lerbäcken, Dlr</t>
+          <t>Kroken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541911</v>
+        <v>542086</v>
       </c>
       <c r="R47" t="n">
-        <v>6712029</v>
+        <v>6712209</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6778,7 +6772,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6788,7 +6782,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Vid vägkant</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6797,6 +6796,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6820,7 +6820,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123830750</v>
+        <v>123831817</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6856,14 +6856,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541959</v>
+        <v>541838</v>
       </c>
       <c r="R48" t="n">
-        <v>6712101</v>
+        <v>6711732</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6932,7 +6932,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123831759</v>
+        <v>123831066</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6968,14 +6968,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torvströmyran, Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika , Torvströmyran, Kroken, Vika , Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541837</v>
+        <v>541923</v>
       </c>
       <c r="R49" t="n">
-        <v>6711742</v>
+        <v>6712001</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7044,7 +7044,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123831817</v>
+        <v>123831788</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -7084,10 +7084,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541838</v>
+        <v>541839</v>
       </c>
       <c r="R50" t="n">
-        <v>6711732</v>
+        <v>6711731</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7156,7 +7156,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123831788</v>
+        <v>123830750</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7192,14 +7192,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Torvströmyran, Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541839</v>
+        <v>541959</v>
       </c>
       <c r="R51" t="n">
-        <v>6711731</v>
+        <v>6712101</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7268,7 +7268,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123831066</v>
+        <v>123831759</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7304,14 +7304,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika , Torvströmyran, Kroken, Vika , Dlr</t>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541923</v>
+        <v>541837</v>
       </c>
       <c r="R52" t="n">
-        <v>6712001</v>
+        <v>6711742</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 13367-2025 artfynd.xlsx
+++ b/artfynd/A 13367-2025 artfynd.xlsx
@@ -6820,7 +6820,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123831817</v>
+        <v>123830750</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6856,14 +6856,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvströmyran, Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541838</v>
+        <v>541959</v>
       </c>
       <c r="R48" t="n">
-        <v>6711732</v>
+        <v>6712101</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6932,7 +6932,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123831066</v>
+        <v>123831759</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6968,14 +6968,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika , Torvströmyran, Kroken, Vika , Dlr</t>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541923</v>
+        <v>541837</v>
       </c>
       <c r="R49" t="n">
-        <v>6712001</v>
+        <v>6711742</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7044,7 +7044,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123831788</v>
+        <v>123831066</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -7080,14 +7080,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Torvströmyran, Torvströmyran, Dlr</t>
+          <t>Torvströmyran, Kroken, Vika , Torvströmyran, Kroken, Vika , Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541839</v>
+        <v>541923</v>
       </c>
       <c r="R50" t="n">
-        <v>6711731</v>
+        <v>6712001</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7156,7 +7156,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123830750</v>
+        <v>123831817</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7192,14 +7192,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Torvströmyran, Kroken, Vika, Torvströmyran, Kroken, Vika, Dlr</t>
+          <t>Torvströmyran, Torvströmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541959</v>
+        <v>541838</v>
       </c>
       <c r="R51" t="n">
-        <v>6712101</v>
+        <v>6711732</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7268,7 +7268,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123831759</v>
+        <v>123831788</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541837</v>
+        <v>541839</v>
       </c>
       <c r="R52" t="n">
-        <v>6711742</v>
+        <v>6711731</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
